--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B22938A-C197-47D5-9309-A3DE2C60AC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F899401-4A5E-4CE0-82B1-6E0B9A438C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,96 +20,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-041971</t>
-  </si>
-  <si>
-    <t>LP-044482</t>
-  </si>
-  <si>
-    <t>LP-045310</t>
-  </si>
-  <si>
-    <t>LP-046159</t>
-  </si>
-  <si>
-    <t>LP-046178</t>
-  </si>
-  <si>
-    <t>LP-046930</t>
-  </si>
-  <si>
-    <t>LP-047775</t>
-  </si>
-  <si>
-    <t>LP-047838</t>
-  </si>
-  <si>
-    <t>LP-048152</t>
-  </si>
-  <si>
-    <t>LP-048175</t>
-  </si>
-  <si>
-    <t>LP-048262</t>
-  </si>
-  <si>
-    <t>LP-048973</t>
-  </si>
-  <si>
-    <t>LP-048974</t>
-  </si>
-  <si>
-    <t>LP-048987</t>
-  </si>
-  <si>
-    <t>LP-048998</t>
-  </si>
-  <si>
-    <t>LP-049168</t>
-  </si>
-  <si>
-    <t>LP-049179</t>
-  </si>
-  <si>
-    <t>LP-049312</t>
-  </si>
-  <si>
-    <t>LP-049457</t>
-  </si>
-  <si>
-    <t>LP-049473</t>
-  </si>
-  <si>
-    <t>LP-049658</t>
-  </si>
-  <si>
-    <t>LP-049757</t>
-  </si>
-  <si>
-    <t>LP-049769</t>
-  </si>
-  <si>
-    <t>LP-049861</t>
-  </si>
-  <si>
-    <t>LP-049942</t>
-  </si>
-  <si>
-    <t>LP-049501</t>
-  </si>
-  <si>
-    <t>LP-049332</t>
-  </si>
-  <si>
-    <t>LP-049003</t>
-  </si>
-  <si>
-    <t>LP-047248</t>
+    <t>LP-046948</t>
+  </si>
+  <si>
+    <t>LP-046959</t>
+  </si>
+  <si>
+    <t>LP-047189</t>
+  </si>
+  <si>
+    <t>LP-048738</t>
+  </si>
+  <si>
+    <t>LP-048762</t>
+  </si>
+  <si>
+    <t>LP-049028</t>
+  </si>
+  <si>
+    <t>LP-049042</t>
+  </si>
+  <si>
+    <t>LP-049048</t>
+  </si>
+  <si>
+    <t>LP-049115</t>
+  </si>
+  <si>
+    <t>LP-049207</t>
+  </si>
+  <si>
+    <t>LP-049208</t>
+  </si>
+  <si>
+    <t>LP-049451</t>
+  </si>
+  <si>
+    <t>LP-049454</t>
+  </si>
+  <si>
+    <t>LP-049670</t>
+  </si>
+  <si>
+    <t>LP-049672</t>
+  </si>
+  <si>
+    <t>LP-049675</t>
+  </si>
+  <si>
+    <t>LP-049683</t>
+  </si>
+  <si>
+    <t>LP-050491</t>
+  </si>
+  <si>
+    <t>LP-042596</t>
   </si>
 </sst>
 </file>
@@ -472,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -485,37 +455,37 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -565,67 +535,17 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F899401-4A5E-4CE0-82B1-6E0B9A438C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7EEDB0-A4C6-4160-BCC4-714CE01297AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,66 +20,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-046948</t>
-  </si>
-  <si>
-    <t>LP-046959</t>
-  </si>
-  <si>
-    <t>LP-047189</t>
-  </si>
-  <si>
-    <t>LP-048738</t>
-  </si>
-  <si>
-    <t>LP-048762</t>
-  </si>
-  <si>
-    <t>LP-049028</t>
-  </si>
-  <si>
-    <t>LP-049042</t>
-  </si>
-  <si>
-    <t>LP-049048</t>
-  </si>
-  <si>
-    <t>LP-049115</t>
-  </si>
-  <si>
-    <t>LP-049207</t>
-  </si>
-  <si>
-    <t>LP-049208</t>
-  </si>
-  <si>
-    <t>LP-049451</t>
-  </si>
-  <si>
-    <t>LP-049454</t>
-  </si>
-  <si>
-    <t>LP-049670</t>
-  </si>
-  <si>
-    <t>LP-049672</t>
-  </si>
-  <si>
-    <t>LP-049675</t>
-  </si>
-  <si>
-    <t>LP-049683</t>
-  </si>
-  <si>
-    <t>LP-050491</t>
-  </si>
-  <si>
-    <t>LP-042596</t>
+    <t>LP-039073</t>
+  </si>
+  <si>
+    <t>LP-046105</t>
+  </si>
+  <si>
+    <t>LP-046956</t>
+  </si>
+  <si>
+    <t>LP-047519</t>
+  </si>
+  <si>
+    <t>LP-047644</t>
+  </si>
+  <si>
+    <t>LP-047828</t>
+  </si>
+  <si>
+    <t>LP-048165</t>
+  </si>
+  <si>
+    <t>LP-048166</t>
+  </si>
+  <si>
+    <t>LP-048649</t>
+  </si>
+  <si>
+    <t>LP-048978</t>
+  </si>
+  <si>
+    <t>LP-049197</t>
+  </si>
+  <si>
+    <t>LP-049211</t>
+  </si>
+  <si>
+    <t>LP-049348</t>
+  </si>
+  <si>
+    <t>LP-049450</t>
+  </si>
+  <si>
+    <t>LP-049453</t>
+  </si>
+  <si>
+    <t>LP-049455</t>
+  </si>
+  <si>
+    <t>LP-049500</t>
+  </si>
+  <si>
+    <t>LP-049674</t>
   </si>
 </sst>
 </file>
@@ -442,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -455,96 +452,91 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,75 +8,133 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7EEDB0-A4C6-4160-BCC4-714CE01297AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282058C4-1144-4FCD-B8E1-C526D5DC1D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-039073</t>
-  </si>
-  <si>
-    <t>LP-046105</t>
-  </si>
-  <si>
-    <t>LP-046956</t>
-  </si>
-  <si>
-    <t>LP-047519</t>
-  </si>
-  <si>
-    <t>LP-047644</t>
-  </si>
-  <si>
-    <t>LP-047828</t>
-  </si>
-  <si>
-    <t>LP-048165</t>
-  </si>
-  <si>
-    <t>LP-048166</t>
-  </si>
-  <si>
-    <t>LP-048649</t>
-  </si>
-  <si>
-    <t>LP-048978</t>
-  </si>
-  <si>
-    <t>LP-049197</t>
-  </si>
-  <si>
-    <t>LP-049211</t>
-  </si>
-  <si>
-    <t>LP-049348</t>
-  </si>
-  <si>
-    <t>LP-049450</t>
-  </si>
-  <si>
-    <t>LP-049453</t>
-  </si>
-  <si>
-    <t>LP-049455</t>
-  </si>
-  <si>
-    <t>LP-049500</t>
-  </si>
-  <si>
-    <t>LP-049674</t>
+    <t>LP-046241</t>
+  </si>
+  <si>
+    <t>LP-046243</t>
+  </si>
+  <si>
+    <t>LP-047123</t>
+  </si>
+  <si>
+    <t>LP-047245</t>
+  </si>
+  <si>
+    <t>LP-047776</t>
+  </si>
+  <si>
+    <t>LP-047842</t>
+  </si>
+  <si>
+    <t>LP-048144</t>
+  </si>
+  <si>
+    <t>LP-048197</t>
+  </si>
+  <si>
+    <t>LP-048198</t>
+  </si>
+  <si>
+    <t>LP-048647</t>
+  </si>
+  <si>
+    <t>LP-048648</t>
+  </si>
+  <si>
+    <t>LP-048717</t>
+  </si>
+  <si>
+    <t>LP-048734</t>
+  </si>
+  <si>
+    <t>LP-048768</t>
+  </si>
+  <si>
+    <t>LP-049033</t>
+  </si>
+  <si>
+    <t>LP-049044</t>
+  </si>
+  <si>
+    <t>LP-049355</t>
+  </si>
+  <si>
+    <t>LP-049356</t>
+  </si>
+  <si>
+    <t>LP-049365</t>
+  </si>
+  <si>
+    <t>LP-049502</t>
+  </si>
+  <si>
+    <t>LP-049505</t>
+  </si>
+  <si>
+    <t>LP-049726</t>
+  </si>
+  <si>
+    <t>LP-049766</t>
+  </si>
+  <si>
+    <t>LP-049773</t>
+  </si>
+  <si>
+    <t>LP-049865</t>
+  </si>
+  <si>
+    <t>LP-049971</t>
+  </si>
+  <si>
+    <t>LP-050139</t>
+  </si>
+  <si>
+    <t>LP-050156</t>
+  </si>
+  <si>
+    <t>LP-050258</t>
+  </si>
+  <si>
+    <t>LP-050298</t>
+  </si>
+  <si>
+    <t>LP-050478</t>
+  </si>
+  <si>
+    <t>LP-047183</t>
+  </si>
+  <si>
+    <t>LP-048646</t>
   </si>
 </sst>
 </file>
@@ -439,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -467,77 +525,152 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,133 +8,72 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282058C4-1144-4FCD-B8E1-C526D5DC1D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4C7ABA-7B2C-4358-A0C0-301C9B6D5125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-046241</t>
-  </si>
-  <si>
-    <t>LP-046243</t>
-  </si>
-  <si>
-    <t>LP-047123</t>
-  </si>
-  <si>
-    <t>LP-047245</t>
-  </si>
-  <si>
-    <t>LP-047776</t>
-  </si>
-  <si>
-    <t>LP-047842</t>
-  </si>
-  <si>
-    <t>LP-048144</t>
-  </si>
-  <si>
-    <t>LP-048197</t>
-  </si>
-  <si>
-    <t>LP-048198</t>
-  </si>
-  <si>
-    <t>LP-048647</t>
-  </si>
-  <si>
-    <t>LP-048648</t>
-  </si>
-  <si>
-    <t>LP-048717</t>
-  </si>
-  <si>
-    <t>LP-048734</t>
-  </si>
-  <si>
-    <t>LP-048768</t>
-  </si>
-  <si>
-    <t>LP-049033</t>
-  </si>
-  <si>
-    <t>LP-049044</t>
-  </si>
-  <si>
-    <t>LP-049355</t>
-  </si>
-  <si>
-    <t>LP-049356</t>
-  </si>
-  <si>
-    <t>LP-049365</t>
-  </si>
-  <si>
-    <t>LP-049502</t>
-  </si>
-  <si>
-    <t>LP-049505</t>
-  </si>
-  <si>
-    <t>LP-049726</t>
-  </si>
-  <si>
-    <t>LP-049766</t>
-  </si>
-  <si>
-    <t>LP-049773</t>
-  </si>
-  <si>
-    <t>LP-049865</t>
-  </si>
-  <si>
-    <t>LP-049971</t>
-  </si>
-  <si>
-    <t>LP-050139</t>
-  </si>
-  <si>
-    <t>LP-050156</t>
-  </si>
-  <si>
-    <t>LP-050258</t>
-  </si>
-  <si>
-    <t>LP-050298</t>
-  </si>
-  <si>
-    <t>LP-050478</t>
-  </si>
-  <si>
-    <t>LP-047183</t>
-  </si>
-  <si>
-    <t>LP-048646</t>
+    <t>LP-043689</t>
+  </si>
+  <si>
+    <t>LP-047197</t>
+  </si>
+  <si>
+    <t>LP-048173</t>
+  </si>
+  <si>
+    <t>LP-048269</t>
+  </si>
+  <si>
+    <t>LP-049045</t>
+  </si>
+  <si>
+    <t>LP-049296</t>
+  </si>
+  <si>
+    <t>LP-049317</t>
+  </si>
+  <si>
+    <t>LP-049374</t>
+  </si>
+  <si>
+    <t>LP-049390</t>
+  </si>
+  <si>
+    <t>LP-049503</t>
+  </si>
+  <si>
+    <t>LP-049649</t>
+  </si>
+  <si>
+    <t>LP-049665</t>
+  </si>
+  <si>
+    <t>LP-049756</t>
+  </si>
+  <si>
+    <t>LP-049863</t>
+  </si>
+  <si>
+    <t>LP-050157</t>
+  </si>
+  <si>
+    <t>LP-045882</t>
+  </si>
+  <si>
+    <t>LP-048512</t>
   </si>
 </sst>
 </file>
@@ -497,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -515,17 +454,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -535,32 +474,32 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -591,86 +530,6 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4C7ABA-7B2C-4358-A0C0-301C9B6D5125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2640D3-8EAD-4F05-B70D-B213B8288DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,60 +20,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-043689</t>
-  </si>
-  <si>
-    <t>LP-047197</t>
-  </si>
-  <si>
-    <t>LP-048173</t>
-  </si>
-  <si>
-    <t>LP-048269</t>
-  </si>
-  <si>
-    <t>LP-049045</t>
-  </si>
-  <si>
-    <t>LP-049296</t>
-  </si>
-  <si>
-    <t>LP-049317</t>
-  </si>
-  <si>
-    <t>LP-049374</t>
-  </si>
-  <si>
-    <t>LP-049390</t>
-  </si>
-  <si>
-    <t>LP-049503</t>
-  </si>
-  <si>
-    <t>LP-049649</t>
-  </si>
-  <si>
-    <t>LP-049665</t>
-  </si>
-  <si>
-    <t>LP-049756</t>
-  </si>
-  <si>
-    <t>LP-049863</t>
-  </si>
-  <si>
-    <t>LP-050157</t>
-  </si>
-  <si>
-    <t>LP-045882</t>
-  </si>
-  <si>
-    <t>LP-048512</t>
+    <t>LP-047110</t>
+  </si>
+  <si>
+    <t>LP-048137</t>
+  </si>
+  <si>
+    <t>LP-048219</t>
+  </si>
+  <si>
+    <t>LP-048388</t>
+  </si>
+  <si>
+    <t>LP-048750</t>
+  </si>
+  <si>
+    <t>LP-049002</t>
+  </si>
+  <si>
+    <t>LP-049026</t>
+  </si>
+  <si>
+    <t>LP-049315</t>
+  </si>
+  <si>
+    <t>LP-049321</t>
+  </si>
+  <si>
+    <t>LP-049322</t>
+  </si>
+  <si>
+    <t>LP-049334</t>
+  </si>
+  <si>
+    <t>LP-049391</t>
+  </si>
+  <si>
+    <t>LP-049458</t>
+  </si>
+  <si>
+    <t>LP-049464</t>
+  </si>
+  <si>
+    <t>LP-049660</t>
+  </si>
+  <si>
+    <t>LP-049666</t>
+  </si>
+  <si>
+    <t>LP-049686</t>
+  </si>
+  <si>
+    <t>LP-049692</t>
+  </si>
+  <si>
+    <t>LP-049693</t>
+  </si>
+  <si>
+    <t>LP-049764</t>
+  </si>
+  <si>
+    <t>LP-049767</t>
+  </si>
+  <si>
+    <t>LP-049847</t>
+  </si>
+  <si>
+    <t>LP-049862</t>
+  </si>
+  <si>
+    <t>LP-049935</t>
+  </si>
+  <si>
+    <t>LP-045624</t>
+  </si>
+  <si>
+    <t>LP-050034</t>
+  </si>
+  <si>
+    <t>LP-050035</t>
+  </si>
+  <si>
+    <t>LP-050128</t>
+  </si>
+  <si>
+    <t>LP-050133</t>
+  </si>
+  <si>
+    <t>LP-050142</t>
+  </si>
+  <si>
+    <t>LP-050175</t>
+  </si>
+  <si>
+    <t>LP-050229</t>
+  </si>
+  <si>
+    <t>LP-050230</t>
+  </si>
+  <si>
+    <t>LP-050235</t>
+  </si>
+  <si>
+    <t>LP-050255</t>
+  </si>
+  <si>
+    <t>LP-050275</t>
+  </si>
+  <si>
+    <t>LP-050378</t>
+  </si>
+  <si>
+    <t>LP-050384</t>
+  </si>
+  <si>
+    <t>LP-050385</t>
+  </si>
+  <si>
+    <t>LP-050386</t>
+  </si>
+  <si>
+    <t>LP-050387</t>
+  </si>
+  <si>
+    <t>LP-040589</t>
+  </si>
+  <si>
+    <t>LP-045336</t>
+  </si>
+  <si>
+    <t>LP-046381</t>
+  </si>
+  <si>
+    <t>LP-049313</t>
+  </si>
+  <si>
+    <t>LP-049459</t>
+  </si>
+  <si>
+    <t>LP-049542</t>
   </si>
 </sst>
 </file>
@@ -436,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -449,87 +539,237 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2640D3-8EAD-4F05-B70D-B213B8288DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0946B-C279-4CC5-9D62-69A9B3A68886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,150 +20,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047110</t>
-  </si>
-  <si>
-    <t>LP-048137</t>
-  </si>
-  <si>
-    <t>LP-048219</t>
-  </si>
-  <si>
-    <t>LP-048388</t>
-  </si>
-  <si>
-    <t>LP-048750</t>
-  </si>
-  <si>
-    <t>LP-049002</t>
-  </si>
-  <si>
-    <t>LP-049026</t>
-  </si>
-  <si>
-    <t>LP-049315</t>
-  </si>
-  <si>
-    <t>LP-049321</t>
-  </si>
-  <si>
-    <t>LP-049322</t>
-  </si>
-  <si>
-    <t>LP-049334</t>
-  </si>
-  <si>
-    <t>LP-049391</t>
-  </si>
-  <si>
-    <t>LP-049458</t>
-  </si>
-  <si>
-    <t>LP-049464</t>
-  </si>
-  <si>
-    <t>LP-049660</t>
-  </si>
-  <si>
-    <t>LP-049666</t>
-  </si>
-  <si>
-    <t>LP-049686</t>
-  </si>
-  <si>
-    <t>LP-049692</t>
-  </si>
-  <si>
-    <t>LP-049693</t>
-  </si>
-  <si>
-    <t>LP-049764</t>
-  </si>
-  <si>
-    <t>LP-049767</t>
-  </si>
-  <si>
-    <t>LP-049847</t>
-  </si>
-  <si>
-    <t>LP-049862</t>
-  </si>
-  <si>
-    <t>LP-049935</t>
-  </si>
-  <si>
-    <t>LP-045624</t>
-  </si>
-  <si>
-    <t>LP-050034</t>
-  </si>
-  <si>
-    <t>LP-050035</t>
-  </si>
-  <si>
-    <t>LP-050128</t>
-  </si>
-  <si>
-    <t>LP-050133</t>
-  </si>
-  <si>
-    <t>LP-050142</t>
-  </si>
-  <si>
-    <t>LP-050175</t>
-  </si>
-  <si>
-    <t>LP-050229</t>
-  </si>
-  <si>
-    <t>LP-050230</t>
-  </si>
-  <si>
-    <t>LP-050235</t>
-  </si>
-  <si>
-    <t>LP-050255</t>
-  </si>
-  <si>
-    <t>LP-050275</t>
-  </si>
-  <si>
-    <t>LP-050378</t>
-  </si>
-  <si>
-    <t>LP-050384</t>
-  </si>
-  <si>
-    <t>LP-050385</t>
-  </si>
-  <si>
-    <t>LP-050386</t>
-  </si>
-  <si>
-    <t>LP-050387</t>
-  </si>
-  <si>
-    <t>LP-040589</t>
-  </si>
-  <si>
-    <t>LP-045336</t>
-  </si>
-  <si>
-    <t>LP-046381</t>
-  </si>
-  <si>
-    <t>LP-049313</t>
-  </si>
-  <si>
-    <t>LP-049459</t>
-  </si>
-  <si>
-    <t>LP-049542</t>
+    <t>LP-047469</t>
+  </si>
+  <si>
+    <t>LP-047772</t>
+  </si>
+  <si>
+    <t>LP-047831</t>
+  </si>
+  <si>
+    <t>LP-048378</t>
+  </si>
+  <si>
+    <t>LP-048658</t>
+  </si>
+  <si>
+    <t>LP-048735</t>
+  </si>
+  <si>
+    <t>LP-048736</t>
+  </si>
+  <si>
+    <t>LP-048976</t>
+  </si>
+  <si>
+    <t>LP-048981</t>
+  </si>
+  <si>
+    <t>LP-049324</t>
+  </si>
+  <si>
+    <t>LP-049349</t>
+  </si>
+  <si>
+    <t>LP-049370</t>
+  </si>
+  <si>
+    <t>LP-049384</t>
+  </si>
+  <si>
+    <t>LP-049835</t>
+  </si>
+  <si>
+    <t>LP-049837</t>
+  </si>
+  <si>
+    <t>LP-049844</t>
+  </si>
+  <si>
+    <t>LP-049845</t>
+  </si>
+  <si>
+    <t>LP-049846</t>
+  </si>
+  <si>
+    <t>LP-049859</t>
+  </si>
+  <si>
+    <t>LP-049993</t>
+  </si>
+  <si>
+    <t>LP-050032</t>
+  </si>
+  <si>
+    <t>LP-050033</t>
+  </si>
+  <si>
+    <t>LP-050136</t>
+  </si>
+  <si>
+    <t>LP-050140</t>
+  </si>
+  <si>
+    <t>LP-050236</t>
+  </si>
+  <si>
+    <t>LP-050299</t>
+  </si>
+  <si>
+    <t>LP-050379</t>
   </si>
 </sst>
 </file>
@@ -526,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -539,237 +479,137 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0946B-C279-4CC5-9D62-69A9B3A68886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E27EACD-BE2A-4C4B-9033-4258FE7F762F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,90 +20,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047469</t>
-  </si>
-  <si>
-    <t>LP-047772</t>
-  </si>
-  <si>
-    <t>LP-047831</t>
-  </si>
-  <si>
-    <t>LP-048378</t>
-  </si>
-  <si>
-    <t>LP-048658</t>
-  </si>
-  <si>
-    <t>LP-048735</t>
-  </si>
-  <si>
-    <t>LP-048736</t>
-  </si>
-  <si>
-    <t>LP-048976</t>
-  </si>
-  <si>
-    <t>LP-048981</t>
-  </si>
-  <si>
-    <t>LP-049324</t>
-  </si>
-  <si>
-    <t>LP-049349</t>
-  </si>
-  <si>
-    <t>LP-049370</t>
-  </si>
-  <si>
-    <t>LP-049384</t>
-  </si>
-  <si>
-    <t>LP-049835</t>
-  </si>
-  <si>
-    <t>LP-049837</t>
-  </si>
-  <si>
-    <t>LP-049844</t>
-  </si>
-  <si>
-    <t>LP-049845</t>
-  </si>
-  <si>
-    <t>LP-049846</t>
-  </si>
-  <si>
-    <t>LP-049859</t>
-  </si>
-  <si>
-    <t>LP-049993</t>
-  </si>
-  <si>
-    <t>LP-050032</t>
-  </si>
-  <si>
-    <t>LP-050033</t>
-  </si>
-  <si>
-    <t>LP-050136</t>
-  </si>
-  <si>
-    <t>LP-050140</t>
-  </si>
-  <si>
-    <t>LP-050236</t>
-  </si>
-  <si>
-    <t>LP-050299</t>
-  </si>
-  <si>
-    <t>LP-050379</t>
+    <t>LP-046944</t>
+  </si>
+  <si>
+    <t>LP-047878</t>
+  </si>
+  <si>
+    <t>LP-047992</t>
+  </si>
+  <si>
+    <t>LP-048031</t>
+  </si>
+  <si>
+    <t>LP-048384</t>
+  </si>
+  <si>
+    <t>LP-048997</t>
+  </si>
+  <si>
+    <t>LP-049036</t>
+  </si>
+  <si>
+    <t>LP-049167</t>
+  </si>
+  <si>
+    <t>LP-049175</t>
+  </si>
+  <si>
+    <t>LP-049217</t>
+  </si>
+  <si>
+    <t>LP-049368</t>
+  </si>
+  <si>
+    <t>LP-049376</t>
+  </si>
+  <si>
+    <t>LP-049504</t>
+  </si>
+  <si>
+    <t>LP-049508</t>
+  </si>
+  <si>
+    <t>LP-049715</t>
+  </si>
+  <si>
+    <t>LP-049958</t>
+  </si>
+  <si>
+    <t>LP-049959</t>
+  </si>
+  <si>
+    <t>LP-049960</t>
+  </si>
+  <si>
+    <t>LP-049962</t>
+  </si>
+  <si>
+    <t>LP-049964</t>
+  </si>
+  <si>
+    <t>LP-049965</t>
+  </si>
+  <si>
+    <t>LP-049972</t>
+  </si>
+  <si>
+    <t>LP-050129</t>
+  </si>
+  <si>
+    <t>LP-050177</t>
+  </si>
+  <si>
+    <t>LP-050234</t>
+  </si>
+  <si>
+    <t>LP-050400</t>
+  </si>
+  <si>
+    <t>LP-050654</t>
+  </si>
+  <si>
+    <t>LP-050666</t>
+  </si>
+  <si>
+    <t>LP-050723</t>
+  </si>
+  <si>
+    <t>LP-046242</t>
+  </si>
+  <si>
+    <t>LP-047510</t>
+  </si>
+  <si>
+    <t>LP-049117</t>
+  </si>
+  <si>
+    <t>LP-050254</t>
+  </si>
+  <si>
+    <t>LP-050668</t>
   </si>
 </sst>
 </file>
@@ -466,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -479,137 +500,172 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E27EACD-BE2A-4C4B-9033-4258FE7F762F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D5A6BF-2F99-4235-914A-76A0B20A9778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,111 +20,165 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-046944</t>
-  </si>
-  <si>
-    <t>LP-047878</t>
-  </si>
-  <si>
-    <t>LP-047992</t>
-  </si>
-  <si>
-    <t>LP-048031</t>
-  </si>
-  <si>
-    <t>LP-048384</t>
-  </si>
-  <si>
-    <t>LP-048997</t>
-  </si>
-  <si>
-    <t>LP-049036</t>
-  </si>
-  <si>
-    <t>LP-049167</t>
-  </si>
-  <si>
-    <t>LP-049175</t>
-  </si>
-  <si>
-    <t>LP-049217</t>
-  </si>
-  <si>
-    <t>LP-049368</t>
-  </si>
-  <si>
-    <t>LP-049376</t>
-  </si>
-  <si>
-    <t>LP-049504</t>
-  </si>
-  <si>
-    <t>LP-049508</t>
-  </si>
-  <si>
-    <t>LP-049715</t>
-  </si>
-  <si>
-    <t>LP-049958</t>
-  </si>
-  <si>
-    <t>LP-049959</t>
-  </si>
-  <si>
-    <t>LP-049960</t>
-  </si>
-  <si>
-    <t>LP-049962</t>
-  </si>
-  <si>
-    <t>LP-049964</t>
-  </si>
-  <si>
-    <t>LP-049965</t>
-  </si>
-  <si>
-    <t>LP-049972</t>
-  </si>
-  <si>
-    <t>LP-050129</t>
-  </si>
-  <si>
-    <t>LP-050177</t>
-  </si>
-  <si>
-    <t>LP-050234</t>
-  </si>
-  <si>
-    <t>LP-050400</t>
-  </si>
-  <si>
-    <t>LP-050654</t>
-  </si>
-  <si>
-    <t>LP-050666</t>
-  </si>
-  <si>
-    <t>LP-050723</t>
-  </si>
-  <si>
-    <t>LP-046242</t>
-  </si>
-  <si>
-    <t>LP-047510</t>
-  </si>
-  <si>
-    <t>LP-049117</t>
-  </si>
-  <si>
-    <t>LP-050254</t>
-  </si>
-  <si>
-    <t>LP-050668</t>
+    <t>LP-042414</t>
+  </si>
+  <si>
+    <t>LP-042416</t>
+  </si>
+  <si>
+    <t>LP-043549</t>
+  </si>
+  <si>
+    <t>LP-044901</t>
+  </si>
+  <si>
+    <t>LP-045346</t>
+  </si>
+  <si>
+    <t>LP-045347</t>
+  </si>
+  <si>
+    <t>LP-046170</t>
+  </si>
+  <si>
+    <t>LP-046338</t>
+  </si>
+  <si>
+    <t>LP-046931</t>
+  </si>
+  <si>
+    <t>LP-047284</t>
+  </si>
+  <si>
+    <t>LP-047334</t>
+  </si>
+  <si>
+    <t>LP-047479</t>
+  </si>
+  <si>
+    <t>LP-047643</t>
+  </si>
+  <si>
+    <t>LP-048273</t>
+  </si>
+  <si>
+    <t>LP-048754</t>
+  </si>
+  <si>
+    <t>LP-048767</t>
+  </si>
+  <si>
+    <t>LP-048979</t>
+  </si>
+  <si>
+    <t>LP-048986</t>
+  </si>
+  <si>
+    <t>LP-049314</t>
+  </si>
+  <si>
+    <t>LP-049327</t>
+  </si>
+  <si>
+    <t>LP-049331</t>
+  </si>
+  <si>
+    <t>LP-049337</t>
+  </si>
+  <si>
+    <t>LP-049360</t>
+  </si>
+  <si>
+    <t>LP-049361</t>
+  </si>
+  <si>
+    <t>LP-049378</t>
+  </si>
+  <si>
+    <t>LP-049379</t>
+  </si>
+  <si>
+    <t>LP-049385</t>
+  </si>
+  <si>
+    <t>LP-049392</t>
+  </si>
+  <si>
+    <t>LP-049393</t>
+  </si>
+  <si>
+    <t>LP-049661</t>
+  </si>
+  <si>
+    <t>LP-049662</t>
+  </si>
+  <si>
+    <t>LP-049689</t>
+  </si>
+  <si>
+    <t>LP-049777</t>
+  </si>
+  <si>
+    <t>LP-049849</t>
+  </si>
+  <si>
+    <t>LP-049957</t>
+  </si>
+  <si>
+    <t>LP-049961</t>
+  </si>
+  <si>
+    <t>LP-049967</t>
+  </si>
+  <si>
+    <t>LP-049994</t>
+  </si>
+  <si>
+    <t>LP-050141</t>
+  </si>
+  <si>
+    <t>LP-050154</t>
+  </si>
+  <si>
+    <t>LP-050232</t>
+  </si>
+  <si>
+    <t>LP-050241</t>
+  </si>
+  <si>
+    <t>LP-050435</t>
+  </si>
+  <si>
+    <t>LP-050463</t>
+  </si>
+  <si>
+    <t>LP-050464</t>
+  </si>
+  <si>
+    <t>LP-050715</t>
+  </si>
+  <si>
+    <t>LP-050759</t>
+  </si>
+  <si>
+    <t>LP-050864</t>
+  </si>
+  <si>
+    <t>LP-050979</t>
+  </si>
+  <si>
+    <t>LP-050130</t>
+  </si>
+  <si>
+    <t>LP-050144</t>
+  </si>
+  <si>
+    <t>LP-050716</t>
   </si>
 </sst>
 </file>
@@ -487,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -500,172 +554,262 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D5A6BF-2F99-4235-914A-76A0B20A9778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44767C2D-028F-4703-8682-698EFA63BA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,165 +20,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-042414</t>
-  </si>
-  <si>
-    <t>LP-042416</t>
-  </si>
-  <si>
-    <t>LP-043549</t>
-  </si>
-  <si>
-    <t>LP-044901</t>
-  </si>
-  <si>
-    <t>LP-045346</t>
-  </si>
-  <si>
-    <t>LP-045347</t>
-  </si>
-  <si>
-    <t>LP-046170</t>
-  </si>
-  <si>
-    <t>LP-046338</t>
-  </si>
-  <si>
-    <t>LP-046931</t>
-  </si>
-  <si>
-    <t>LP-047284</t>
-  </si>
-  <si>
-    <t>LP-047334</t>
-  </si>
-  <si>
-    <t>LP-047479</t>
-  </si>
-  <si>
-    <t>LP-047643</t>
-  </si>
-  <si>
-    <t>LP-048273</t>
-  </si>
-  <si>
-    <t>LP-048754</t>
-  </si>
-  <si>
-    <t>LP-048767</t>
-  </si>
-  <si>
-    <t>LP-048979</t>
-  </si>
-  <si>
-    <t>LP-048986</t>
-  </si>
-  <si>
-    <t>LP-049314</t>
-  </si>
-  <si>
-    <t>LP-049327</t>
-  </si>
-  <si>
-    <t>LP-049331</t>
-  </si>
-  <si>
-    <t>LP-049337</t>
-  </si>
-  <si>
-    <t>LP-049360</t>
-  </si>
-  <si>
-    <t>LP-049361</t>
-  </si>
-  <si>
-    <t>LP-049378</t>
-  </si>
-  <si>
-    <t>LP-049379</t>
-  </si>
-  <si>
-    <t>LP-049385</t>
-  </si>
-  <si>
-    <t>LP-049392</t>
-  </si>
-  <si>
-    <t>LP-049393</t>
-  </si>
-  <si>
-    <t>LP-049661</t>
-  </si>
-  <si>
-    <t>LP-049662</t>
-  </si>
-  <si>
-    <t>LP-049689</t>
-  </si>
-  <si>
-    <t>LP-049777</t>
-  </si>
-  <si>
-    <t>LP-049849</t>
-  </si>
-  <si>
-    <t>LP-049957</t>
-  </si>
-  <si>
-    <t>LP-049961</t>
-  </si>
-  <si>
-    <t>LP-049967</t>
-  </si>
-  <si>
-    <t>LP-049994</t>
-  </si>
-  <si>
-    <t>LP-050141</t>
-  </si>
-  <si>
-    <t>LP-050154</t>
-  </si>
-  <si>
-    <t>LP-050232</t>
-  </si>
-  <si>
-    <t>LP-050241</t>
-  </si>
-  <si>
-    <t>LP-050435</t>
-  </si>
-  <si>
-    <t>LP-050463</t>
-  </si>
-  <si>
-    <t>LP-050464</t>
-  </si>
-  <si>
-    <t>LP-050715</t>
-  </si>
-  <si>
-    <t>LP-050759</t>
-  </si>
-  <si>
-    <t>LP-050864</t>
-  </si>
-  <si>
-    <t>LP-050979</t>
-  </si>
-  <si>
-    <t>LP-050130</t>
-  </si>
-  <si>
-    <t>LP-050144</t>
-  </si>
-  <si>
-    <t>LP-050716</t>
+    <t>LP-046342</t>
+  </si>
+  <si>
+    <t>LP-046346</t>
+  </si>
+  <si>
+    <t>LP-046957</t>
+  </si>
+  <si>
+    <t>LP-048167</t>
+  </si>
+  <si>
+    <t>LP-048749</t>
+  </si>
+  <si>
+    <t>LP-048975</t>
+  </si>
+  <si>
+    <t>LP-049118</t>
+  </si>
+  <si>
+    <t>LP-049344</t>
+  </si>
+  <si>
+    <t>LP-049353</t>
+  </si>
+  <si>
+    <t>LP-049357</t>
+  </si>
+  <si>
+    <t>LP-049364</t>
+  </si>
+  <si>
+    <t>LP-049387</t>
+  </si>
+  <si>
+    <t>LP-049518</t>
+  </si>
+  <si>
+    <t>LP-049648</t>
+  </si>
+  <si>
+    <t>LP-049669</t>
+  </si>
+  <si>
+    <t>LP-049765</t>
+  </si>
+  <si>
+    <t>LP-049842</t>
+  </si>
+  <si>
+    <t>LP-049848</t>
+  </si>
+  <si>
+    <t>LP-049934</t>
+  </si>
+  <si>
+    <t>LP-050086</t>
+  </si>
+  <si>
+    <t>LP-050131</t>
+  </si>
+  <si>
+    <t>LP-050159</t>
+  </si>
+  <si>
+    <t>LP-050160</t>
+  </si>
+  <si>
+    <t>LP-050376</t>
+  </si>
+  <si>
+    <t>LP-050382</t>
+  </si>
+  <si>
+    <t>LP-050383</t>
+  </si>
+  <si>
+    <t>LP-050389</t>
+  </si>
+  <si>
+    <t>LP-050392</t>
+  </si>
+  <si>
+    <t>LP-050428</t>
+  </si>
+  <si>
+    <t>LP-050518</t>
+  </si>
+  <si>
+    <t>LP-050670</t>
+  </si>
+  <si>
+    <t>LP-050714</t>
+  </si>
+  <si>
+    <t>LP-050722</t>
+  </si>
+  <si>
+    <t>LP-050732</t>
+  </si>
+  <si>
+    <t>LP-050733</t>
+  </si>
+  <si>
+    <t>LP-050734</t>
+  </si>
+  <si>
+    <t>LP-050754</t>
+  </si>
+  <si>
+    <t>LP-050857</t>
+  </si>
+  <si>
+    <t>LP-050894</t>
+  </si>
+  <si>
+    <t>LP-049173</t>
+  </si>
+  <si>
+    <t>LP-049358</t>
+  </si>
+  <si>
+    <t>LP-050519</t>
   </si>
 </sst>
 </file>
@@ -541,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -589,227 +559,177 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44767C2D-028F-4703-8682-698EFA63BA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6D467E-C61E-4177-97AC-65E50EC91D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,135 +20,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-046342</t>
-  </si>
-  <si>
-    <t>LP-046346</t>
-  </si>
-  <si>
-    <t>LP-046957</t>
-  </si>
-  <si>
-    <t>LP-048167</t>
-  </si>
-  <si>
-    <t>LP-048749</t>
-  </si>
-  <si>
-    <t>LP-048975</t>
-  </si>
-  <si>
-    <t>LP-049118</t>
-  </si>
-  <si>
-    <t>LP-049344</t>
-  </si>
-  <si>
-    <t>LP-049353</t>
-  </si>
-  <si>
-    <t>LP-049357</t>
-  </si>
-  <si>
-    <t>LP-049364</t>
-  </si>
-  <si>
-    <t>LP-049387</t>
-  </si>
-  <si>
-    <t>LP-049518</t>
-  </si>
-  <si>
-    <t>LP-049648</t>
-  </si>
-  <si>
-    <t>LP-049669</t>
-  </si>
-  <si>
-    <t>LP-049765</t>
-  </si>
-  <si>
-    <t>LP-049842</t>
-  </si>
-  <si>
-    <t>LP-049848</t>
-  </si>
-  <si>
-    <t>LP-049934</t>
-  </si>
-  <si>
-    <t>LP-050086</t>
-  </si>
-  <si>
-    <t>LP-050131</t>
-  </si>
-  <si>
-    <t>LP-050159</t>
-  </si>
-  <si>
-    <t>LP-050160</t>
-  </si>
-  <si>
-    <t>LP-050376</t>
-  </si>
-  <si>
-    <t>LP-050382</t>
-  </si>
-  <si>
-    <t>LP-050383</t>
-  </si>
-  <si>
-    <t>LP-050389</t>
-  </si>
-  <si>
-    <t>LP-050392</t>
-  </si>
-  <si>
-    <t>LP-050428</t>
-  </si>
-  <si>
-    <t>LP-050518</t>
-  </si>
-  <si>
-    <t>LP-050670</t>
-  </si>
-  <si>
-    <t>LP-050714</t>
-  </si>
-  <si>
-    <t>LP-050722</t>
-  </si>
-  <si>
-    <t>LP-050732</t>
-  </si>
-  <si>
-    <t>LP-050733</t>
-  </si>
-  <si>
-    <t>LP-050734</t>
-  </si>
-  <si>
-    <t>LP-050754</t>
-  </si>
-  <si>
-    <t>LP-050857</t>
-  </si>
-  <si>
-    <t>LP-050894</t>
-  </si>
-  <si>
-    <t>LP-049173</t>
-  </si>
-  <si>
-    <t>LP-049358</t>
-  </si>
-  <si>
-    <t>LP-050519</t>
+    <t>LP-041815</t>
+  </si>
+  <si>
+    <t>LP-047203</t>
+  </si>
+  <si>
+    <t>LP-047247</t>
+  </si>
+  <si>
+    <t>LP-047835</t>
+  </si>
+  <si>
+    <t>LP-047887</t>
+  </si>
+  <si>
+    <t>LP-047888</t>
+  </si>
+  <si>
+    <t>LP-048163</t>
+  </si>
+  <si>
+    <t>LP-048189</t>
+  </si>
+  <si>
+    <t>LP-048220</t>
+  </si>
+  <si>
+    <t>LP-048659</t>
+  </si>
+  <si>
+    <t>LP-048984</t>
+  </si>
+  <si>
+    <t>LP-048996</t>
+  </si>
+  <si>
+    <t>LP-049690</t>
+  </si>
+  <si>
+    <t>LP-049691</t>
+  </si>
+  <si>
+    <t>LP-049841</t>
+  </si>
+  <si>
+    <t>LP-049870</t>
+  </si>
+  <si>
+    <t>LP-049871</t>
+  </si>
+  <si>
+    <t>LP-049954</t>
+  </si>
+  <si>
+    <t>LP-050088</t>
+  </si>
+  <si>
+    <t>LP-050089</t>
+  </si>
+  <si>
+    <t>LP-050433</t>
+  </si>
+  <si>
+    <t>LP-050436</t>
+  </si>
+  <si>
+    <t>LP-050475</t>
+  </si>
+  <si>
+    <t>LP-050477</t>
+  </si>
+  <si>
+    <t>LP-050528</t>
+  </si>
+  <si>
+    <t>LP-050551</t>
+  </si>
+  <si>
+    <t>LP-050724</t>
+  </si>
+  <si>
+    <t>LP-050981</t>
+  </si>
+  <si>
+    <t>LP-051307</t>
+  </si>
+  <si>
+    <t>LP-049840</t>
+  </si>
+  <si>
+    <t>LP-050059</t>
+  </si>
+  <si>
+    <t>LP-050064</t>
   </si>
 </sst>
 </file>
@@ -511,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -559,177 +529,127 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - pé.xlsx
+++ b/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6D467E-C61E-4177-97AC-65E50EC91D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71100672-0DEA-48D3-AA5D-1190799CAF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,105 +20,219 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-041815</t>
-  </si>
-  <si>
-    <t>LP-047203</t>
-  </si>
-  <si>
-    <t>LP-047247</t>
-  </si>
-  <si>
-    <t>LP-047835</t>
-  </si>
-  <si>
-    <t>LP-047887</t>
-  </si>
-  <si>
-    <t>LP-047888</t>
-  </si>
-  <si>
-    <t>LP-048163</t>
-  </si>
-  <si>
-    <t>LP-048189</t>
-  </si>
-  <si>
-    <t>LP-048220</t>
-  </si>
-  <si>
-    <t>LP-048659</t>
-  </si>
-  <si>
-    <t>LP-048984</t>
-  </si>
-  <si>
-    <t>LP-048996</t>
-  </si>
-  <si>
-    <t>LP-049690</t>
-  </si>
-  <si>
-    <t>LP-049691</t>
-  </si>
-  <si>
-    <t>LP-049841</t>
-  </si>
-  <si>
-    <t>LP-049870</t>
-  </si>
-  <si>
-    <t>LP-049871</t>
-  </si>
-  <si>
-    <t>LP-049954</t>
-  </si>
-  <si>
-    <t>LP-050088</t>
-  </si>
-  <si>
-    <t>LP-050089</t>
-  </si>
-  <si>
-    <t>LP-050433</t>
-  </si>
-  <si>
-    <t>LP-050436</t>
-  </si>
-  <si>
-    <t>LP-050475</t>
-  </si>
-  <si>
-    <t>LP-050477</t>
-  </si>
-  <si>
-    <t>LP-050528</t>
-  </si>
-  <si>
-    <t>LP-050551</t>
-  </si>
-  <si>
-    <t>LP-050724</t>
-  </si>
-  <si>
-    <t>LP-050981</t>
-  </si>
-  <si>
-    <t>LP-051307</t>
-  </si>
-  <si>
-    <t>LP-049840</t>
-  </si>
-  <si>
-    <t>LP-050059</t>
-  </si>
-  <si>
-    <t>LP-050064</t>
+    <t>LP-044816</t>
+  </si>
+  <si>
+    <t>LP-045910</t>
+  </si>
+  <si>
+    <t>LP-046171</t>
+  </si>
+  <si>
+    <t>LP-046811</t>
+  </si>
+  <si>
+    <t>LP-047333</t>
+  </si>
+  <si>
+    <t>LP-047840</t>
+  </si>
+  <si>
+    <t>LP-048259</t>
+  </si>
+  <si>
+    <t>LP-048389</t>
+  </si>
+  <si>
+    <t>LP-048982</t>
+  </si>
+  <si>
+    <t>LP-049000</t>
+  </si>
+  <si>
+    <t>LP-049035</t>
+  </si>
+  <si>
+    <t>LP-049119</t>
+  </si>
+  <si>
+    <t>LP-049142</t>
+  </si>
+  <si>
+    <t>LP-049162</t>
+  </si>
+  <si>
+    <t>LP-049333</t>
+  </si>
+  <si>
+    <t>LP-049347</t>
+  </si>
+  <si>
+    <t>LP-049359</t>
+  </si>
+  <si>
+    <t>LP-049375</t>
+  </si>
+  <si>
+    <t>LP-049383</t>
+  </si>
+  <si>
+    <t>LP-049465</t>
+  </si>
+  <si>
+    <t>LP-049507</t>
+  </si>
+  <si>
+    <t>LP-049663</t>
+  </si>
+  <si>
+    <t>LP-049664</t>
+  </si>
+  <si>
+    <t>LP-049667</t>
+  </si>
+  <si>
+    <t>LP-049771</t>
+  </si>
+  <si>
+    <t>LP-049772</t>
+  </si>
+  <si>
+    <t>LP-049850</t>
+  </si>
+  <si>
+    <t>LP-549852</t>
+  </si>
+  <si>
+    <t>LP-049969</t>
+  </si>
+  <si>
+    <t>LP-050125</t>
+  </si>
+  <si>
+    <t>LP-050155</t>
+  </si>
+  <si>
+    <t>LP-050276</t>
+  </si>
+  <si>
+    <t>LP-050393</t>
+  </si>
+  <si>
+    <t>LP-050402</t>
+  </si>
+  <si>
+    <t>LP-050434</t>
+  </si>
+  <si>
+    <t>LP-050437</t>
+  </si>
+  <si>
+    <t>LP-050471</t>
+  </si>
+  <si>
+    <t>LP-050719</t>
+  </si>
+  <si>
+    <t>LP-050721</t>
+  </si>
+  <si>
+    <t>LP-050749</t>
+  </si>
+  <si>
+    <t>LP-050751</t>
+  </si>
+  <si>
+    <t>LP-050867</t>
+  </si>
+  <si>
+    <t>LP-051076</t>
+  </si>
+  <si>
+    <t>LP-051078</t>
+  </si>
+  <si>
+    <t>LP-051081</t>
+  </si>
+  <si>
+    <t>LP-051084</t>
+  </si>
+  <si>
+    <t>LP-051138</t>
+  </si>
+  <si>
+    <t>LP-051157</t>
+  </si>
+  <si>
+    <t>LP-051158</t>
+  </si>
+  <si>
+    <t>LP-051256</t>
+  </si>
+  <si>
+    <t>LP-051282</t>
+  </si>
+  <si>
+    <t>LP-051283</t>
+  </si>
+  <si>
+    <t>LP-051300</t>
+  </si>
+  <si>
+    <t>LP-051301</t>
+  </si>
+  <si>
+    <t>LP-051423</t>
+  </si>
+  <si>
+    <t>LP-051520</t>
+  </si>
+  <si>
+    <t>LP-051522</t>
+  </si>
+  <si>
+    <t>LP-051539</t>
+  </si>
+  <si>
+    <t>LP-051545</t>
+  </si>
+  <si>
+    <t>LP-051718</t>
+  </si>
+  <si>
+    <t>LP-051719</t>
+  </si>
+  <si>
+    <t>LP-051729</t>
+  </si>
+  <si>
+    <t>LP-052098</t>
+  </si>
+  <si>
+    <t>LP-049343</t>
+  </si>
+  <si>
+    <t>LP-049970</t>
+  </si>
+  <si>
+    <t>LP-050256</t>
+  </si>
+  <si>
+    <t>LP-050414</t>
+  </si>
+  <si>
+    <t>LP-051087</t>
+  </si>
+  <si>
+    <t>LP-051492</t>
+  </si>
+  <si>
+    <t>LP-051728</t>
   </si>
 </sst>
 </file>
@@ -481,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -564,12 +678,12 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -589,67 +703,257 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
